--- a/build/fees-discounts/FeesAndDiscounts_TraceabilityStatus_2026-07-22.xlsx
+++ b/build/fees-discounts/FeesAndDiscounts_TraceabilityStatus_2026-07-22.xlsx
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>186 cases in scope · 186 Traceable (per-story ticket set in TestRail refs) · 0 flagged (id-map C-ID absent in live TestRail). Spec anchor: https://shopview.atlassian.net/wiki/spaces/~712020aa00b8d6a71f4259891982a304227c20/pages/622297094</t>
+          <t>186 cases in scope · 186 Traceable (per-story ticket + spec anchor together in TestRail refs) · 0 ignored per user 2026-07-22 (id-map C-ID absent in live TestRail). Spec: https://shopview.atlassian.net/wiki/spaces/~712020aa00b8d6a71f4259891982a304227c20/pages/622297094</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ticket refs (set)</t>
+          <t>refs — ticket + spec (set)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>SV-7865</t>
+          <t>SV-7865 (§5-R3)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>SV-7865</t>
+          <t>SV-7865 (§5-R3)</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>SV-7865</t>
+          <t>SV-7865 (§5-R14)</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>SV-7865</t>
+          <t>SV-7865 (§5-R14)</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>SV-7865</t>
+          <t>SV-7865 (§5-R2)</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>SV-7865</t>
+          <t>SV-7865 (§5-R1)</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>SV-7865</t>
+          <t>SV-7865 (§5-R6)</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>SV-7865</t>
+          <t>SV-7865 (§5-R6)</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>SV-7865</t>
+          <t>SV-7865 (§5-R8)</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>SV-7865</t>
+          <t>SV-7865 (§5-R3, §5-R4)</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>SV-7865</t>
+          <t>SV-7865 (§5-R11)</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>SV-7865</t>
+          <t>SV-7865 (§5-R5)</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>SV-7865</t>
+          <t>SV-7865 (§5-R4, §5-R5)</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>SV-8284</t>
+          <t>SV-8284 (§5-R4, S8-R10)</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>SV-8282</t>
+          <t>SV-8282 (S6-R10, S6-R11, S6-R12, S6-R13)</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>SV-8282</t>
+          <t>SV-8282 (S6-R10c)</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>SV-8282</t>
+          <t>SV-8282 (S6-R10d)</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>SV-8285</t>
+          <t>SV-8285 (S9-R11)</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>SV-8285, SV-8288</t>
+          <t>SV-8285,SV-8288 (S9-R12, S9-R13, S9-R14, S9-R15, S12-R8)</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>SV-8285</t>
+          <t>SV-8285 (S9-R18, S9-R19, S9-R20, S9-R21, S9-R23a)</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>SV-8285</t>
+          <t>SV-8285 (S9-R20, S9-R21, S9-R23a)</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>SV-8284, SV-8285</t>
+          <t>SV-8284,SV-8285 (S9-R19, S8-R15, S9-R... (Processing Fee shows as "Fee"))</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>SV-8285</t>
+          <t>SV-8285 (S9-R22)</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>SV-8285</t>
+          <t>SV-8285 (S9-R16, S9-R24)</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>SV-8285</t>
+          <t>SV-8285 (S9-R17)</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>SV-8285</t>
+          <t>SV-8285 (S9-R2, S9-R3, S9-R4)</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>SV-8285</t>
+          <t>SV-8285 (S9-R6, S9-R7)</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>SV-8285</t>
+          <t>SV-8285 (S9-R8)</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>SV-8283, SV-8285</t>
+          <t>SV-8283,SV-8285 (S9-R9, S7-R4, S7-N1)</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>SV-8285</t>
+          <t>SV-8285 (S9-R10)</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>SV-8285</t>
+          <t>SV-8285 (S9-R1)</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>SV-8289</t>
+          <t>SV-8289 (S13-R9, S13-N3)</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>SV-8285</t>
+          <t>SV-8285 (S9-N1)</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>SV-8281</t>
+          <t>SV-8281 (S5-R1)</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>SV-8281, SV-8288</t>
+          <t>SV-8281,SV-8288 (S5-R2, S5-R3, S5-R4, S12-R3)</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>SV-8281</t>
+          <t>SV-8281 (S5-R2, S5-R3)</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>SV-8281, SV-8288</t>
+          <t>SV-8281,SV-8288 (S5-R4, S5-R9, S12-R7)</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>SV-8281</t>
+          <t>SV-8281 (S5-R5, S5-R6)</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>SV-8281</t>
+          <t>SV-8281 (S5-R7, S5-R8)</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>SV-8281, SV-8284</t>
+          <t>SV-8281,SV-8284 (S5-R6, S8-R22)</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>SV-8290</t>
+          <t>SV-8290 (S14-R1)</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>SV-8290</t>
+          <t>SV-8290 (S14-R2)</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>SV-8281</t>
+          <t>SV-8281 (§5-R12)</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>SV-8281</t>
+          <t>SV-8281 (S5-R5)</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>SV-8278</t>
+          <t>SV-8278 (S2-R4 / S2-R5 / S2-R8)</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>SV-8278</t>
+          <t>SV-8278 (S2-R6 / S2-R7 / S2-R18 / S2-R28)</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>SV-8278</t>
+          <t>SV-8278 (S2-R30)</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>SV-8279</t>
+          <t>SV-8279 (S3-R20 / S3-R21 / S3-R22)</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>SV-8279</t>
+          <t>SV-8279 (S3-R23 / S3-R24 / §5-R9)</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>SV-8279</t>
+          <t>SV-8279 (S3-N2 / S3-N4)</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>SV-8279</t>
+          <t>SV-8279 (S3-R3 / S3-R5 / S3-R8 / S3-R9)</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>SV-8279</t>
+          <t>SV-8279 (S3-R4 / S3-R10 / S3-N1)</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>SV-8289</t>
+          <t>SV-8289 (§1 feature flag, S13-R1)</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>SV-8286</t>
+          <t>SV-8286 (S10-R1 (flag-off exception))</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>SV-8289</t>
+          <t>SV-8289 (§1 feature flag + S13-R1)</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>SV-8286</t>
+          <t>SV-8286 (S10-R2, S10-R4a, S10-R4b, S10-R4c)</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>SV-8286</t>
+          <t>SV-8286 (S10-R6a, S10-R6b, S10-R6c, S10-R6d)</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>SV-8286</t>
+          <t>SV-8286 (S10-R3, S10-R5)</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>SV-8286</t>
+          <t>SV-8286 (S10-R1)</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>SV-8286, SV-8289</t>
+          <t>SV-8286,SV-8289 (S10-R1, S10-R6c, S13-R10)</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>SV-8289</t>
+          <t>SV-8289 (S13-R10)</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>SV-8284, SV-8286</t>
+          <t>SV-8284,SV-8286 (S8-R25, S8-R26, S10 (Processing Fee note))</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>SV-8278, SV-8286</t>
+          <t>SV-8278,SV-8286 (S10-R6c, S2-R6)</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>SV-8279, SV-8288</t>
+          <t>SV-8279,SV-8288 (S3-R12 / S3-R14 / S12-R3)</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>SV-8279</t>
+          <t>SV-8279 (S3-R13 / S3-R14)</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>SV-8279, SV-8288</t>
+          <t>SV-8279,SV-8288 (S3-R15 / S3-R16 / S12-R6)</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>SV-8279</t>
+          <t>SV-8279 (S3-R18 / S3-R19)</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>SV-8279, SV-8288</t>
+          <t>SV-8279,SV-8288 (S3-R17 / S12-R5)</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>SV-8277, SV-8278</t>
+          <t>SV-8277,SV-8278 (S1-R3 / S2-R10)</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>SV-8278</t>
+          <t>SV-8278 (§5-R4 / §5-R3 / S2-R22)</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>SV-8277</t>
+          <t>SV-8277 (S1-R2)</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>SV-8278</t>
+          <t>SV-8278 (§5-R14 / S2-R23)</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>SV-7865</t>
+          <t>SV-7865 (§5-R12)</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>SV-8279</t>
+          <t>SV-8279 (S3-R2)</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>SV-8289</t>
+          <t>SV-8289 (S13-R4 / S13-N2)</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>SV-8277, SV-8278</t>
+          <t>SV-8277,SV-8278 (S1-R4 / S1-R5 / S2-R11)</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>SV-7865</t>
+          <t>SV-7865 (§5-R14)</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>SV-8277</t>
+          <t>SV-8277 (S1-R4 / §5-R13)</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>SV-7865</t>
+          <t>SV-7865 (§5-R4 / §5-R10 / §5-R3)</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>SV-8279</t>
+          <t>SV-8279 (§5-R13)</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>SV-7865</t>
+          <t>SV-7865 (§5-R12)</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>SV-8279</t>
+          <t>SV-8279 (S3-R2)</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>SV-7865</t>
+          <t>SV-7865 (§5-R14)</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>SV-8287</t>
+          <t>SV-8287 (S11-R10a / design §5)</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>SV-8287</t>
+          <t>SV-8287 (S11-R10b / design §5)</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>SV-8287</t>
+          <t>SV-8287 (S11-R9 / design §5)</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>SV-8287</t>
+          <t>SV-8287 (S11-R11 / S11-R12 / S11-R13 / S11-R16)</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>SV-8287</t>
+          <t>SV-8287 (S11-R15)</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>SV-8287</t>
+          <t>SV-8287 (S11-R14 / S11-R17)</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>SV-8279, SV-8287</t>
+          <t>SV-8279,SV-8287 (S11-R9 / S3-R1b)</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>SV-8289</t>
+          <t>SV-8289 (S13-R2, S13-N1)</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>SV-8289</t>
+          <t>SV-8289 (S13-R3)</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>SV-8289</t>
+          <t>SV-8289 (S13-R4)</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>SV-8289</t>
+          <t>SV-8289 (S13-R5)</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>SV-8289</t>
+          <t>SV-8289 (S13-R6)</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>SV-8289</t>
+          <t>SV-8289 (S13-R7)</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>SV-8289</t>
+          <t>SV-8289 (S13-R8)</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>SV-8289</t>
+          <t>SV-8289 (S13-R9, S13-N3)</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>SV-8289</t>
+          <t>SV-8289 (S13-R10)</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>SV-8289</t>
+          <t>SV-8289 (S13-R1, feature flag + permission (both gates))</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>SV-8277, SV-8279</t>
+          <t>SV-8277,SV-8279 (S1-N1, S3-R1b, S3-R1a)</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>SV-8283, SV-8284</t>
+          <t>SV-8283,SV-8284 (S8-R1, S8-R3, S7-R12a)</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>SV-8284</t>
+          <t>SV-8284 (S8-R5, S8-R6, S8-R9, §5-R4, §5-R10)</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>SV-8283, SV-8284</t>
+          <t>SV-8283,SV-8284 (S8-R10, S8-N3, S7-R12e)</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>SV-8284</t>
+          <t>SV-8284 (S8-R11, S8-R12, S8-R13, §5-R15)</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>SV-8284</t>
+          <t>SV-8284 (S8-R16, S8-N1, S8-N2)</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>SV-8283, SV-8284</t>
+          <t>SV-8283,SV-8284 (S8-R14, S7-R5)</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>SV-8284, SV-8285</t>
+          <t>SV-8284,SV-8285 (S8-R15, S9-R2)</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>SV-8279, SV-8284</t>
+          <t>SV-8279,SV-8284 (S8-R17, S8-N5, S3-R9)</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>SV-8284</t>
+          <t>SV-8284 (S8-R5, §5-R4, §5-R5 (Step 3))</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>SV-8284</t>
+          <t>SV-8284 (S8-N4)</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>SV-8284</t>
+          <t>SV-8284 (S8-R2)</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>SV-8284</t>
+          <t>SV-8284 (S8-R18, S8-R19)</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>SV-8284</t>
+          <t>SV-8284 (§5-R4 (multiple Processing Fees))</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>SV-8284</t>
+          <t>SV-8284 (S8-N6)</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>SV-8282</t>
+          <t>SV-8282 (S6-R1)</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>SV-8282</t>
+          <t>SV-8282 (S6-R3, S6-R5)</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>SV-8282</t>
+          <t>SV-8282 (S6-R1, §5-R8)</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>SV-8282</t>
+          <t>SV-8282 (S6-R6, S6-R6a, S6-R6d)</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>SV-8282</t>
+          <t>SV-8282 (S6-R6, S6-R6d)</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>SV-8282</t>
+          <t>SV-8282 (S6-R6a)</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>SV-8282</t>
+          <t>SV-8282 (S6-R6b)</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>SV-8282</t>
+          <t>SV-8282 (S6-R6c)</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>SV-8282</t>
+          <t>SV-8282 (S6-R7, S6-R7a)</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>SV-8282</t>
+          <t>SV-8282 (S6-R8)</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>SV-8282</t>
+          <t>SV-8282 (S6-R9)</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>SV-8282</t>
+          <t>SV-8282 (S6-R10, S6-R10a, S6-R10b, S6-R10c)</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>SV-8282</t>
+          <t>SV-8282 (S6-R10d)</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>SV-8282</t>
+          <t>SV-8282 (S6-R12)</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>SV-8282</t>
+          <t>SV-8282 (S6-R11, S6-R13)</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>SV-8282</t>
+          <t>SV-8282 (S6-R2, §5-R11)</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>SV-8279</t>
+          <t>SV-8279 (S3-R11a / S3-R11b / §7)</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>SV-8289</t>
+          <t>SV-8289 (S13-R7 / S13-N2)</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>SV-8279</t>
+          <t>SV-8279 (S3-R17 / S3-R11a)</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>SV-8279, SV-8287</t>
+          <t>SV-8279,SV-8287 (§5-R5 (Step 1) / S3-R15 / S11-R15)</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>SV-7865</t>
+          <t>SV-7865 (§5-R5 (Step 2) / spec §5 worked example)</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>SV-8283</t>
+          <t>SV-8283 (Overview 'apply same template more than once' / §3 key decisions)</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>SV-8280</t>
+          <t>SV-8280 (S4-R1 / S4-R2 / S4-R3)</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>SV-8280</t>
+          <t>SV-8280 (S4-R3 / design §3)</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>SV-8280</t>
+          <t>SV-8280 (S4-R4 / S4-R6)</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>SV-8280</t>
+          <t>SV-8280 (§5-R9)</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>SV-8280</t>
+          <t>SV-8280 (S4-N1)</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>SV-8283</t>
+          <t>SV-8283 (S7-R7a, S7-R7c)</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>SV-8283, SV-8288</t>
+          <t>SV-8283,SV-8288 (S7-R8, S12-R8)</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>SV-8283</t>
+          <t>SV-8283 (S7-R10, S7-R12a-g, S7-R16, S7-R17, S7-R18a)</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>SV-8283</t>
+          <t>SV-8283 (S7-R12a, S7-R18a)</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>SV-8283</t>
+          <t>SV-8283 (S7-R12g, S7-R5, S7-R6a, S7-R6b)</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>SV-8283</t>
+          <t>SV-8283 (S7-R9, S7-R16, S7-R17, S7-R18b)</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>SV-8283</t>
+          <t>SV-8283 (S7-R20)</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>SV-8283</t>
+          <t>SV-8283 (S7-R21)</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>SV-8283</t>
+          <t>SV-8283 (S7-N1, S7-R4)</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>SV-8278, SV-8281</t>
+          <t>SV-8278,SV-8281 (S2-R14, S2-R15, S2-R16, S5-R10)</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>SV-8283</t>
+          <t>SV-8283 (S7-R12e, S7-R14, §5-R6)</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>SV-8283</t>
+          <t>SV-8283 (S7-R11)</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>SV-8283</t>
+          <t>SV-8283 (S7-R3, §5-R2)</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>SV-8283</t>
+          <t>SV-8283 (S7-R2, S7-R13, S7-R15)</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>SV-8283</t>
+          <t>SV-8283 (S7-R19)</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>SV-8283, SV-8289</t>
+          <t>SV-8283,SV-8289 (S13-R8, S7-R7b)</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>SV-8283</t>
+          <t>SV-8283 (S7-R12c)</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>SV-8278</t>
+          <t>SV-8278 (design §6 (Add-button enable rule); S2-N1, S2-N2)</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>SV-8278</t>
+          <t>SV-8278 (S2-N2, §5-R1)</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>SV-8278</t>
+          <t>SV-8278 (S2-N1, S2-R19)</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>SV-8278</t>
+          <t>SV-8278 (§5-R2)</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>SV-8278</t>
+          <t>SV-8278 (§5-R1)</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>SV-8278</t>
+          <t>SV-8278 (§5-R6, S2-R24, S2-R25)</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>SV-8283, SV-8285</t>
+          <t>SV-8283,SV-8285 (S9 known gap (auto-apply + customer-default duplication); S7-R5, S9-R2)</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>SV-8277, SV-8278</t>
+          <t>SV-8277,SV-8278 (S1-R1 / S2-R9 / S2-R12)</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>SV-8278</t>
+          <t>SV-8278 (S2-R19..R27 / S2-R29 / §7 toast)</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>SV-8278</t>
+          <t>SV-8278 (S2-R31..R35 / §5-R3)</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>SV-8278</t>
+          <t>SV-8278 (S2-R13 / S2-R14)</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>SV-8278</t>
+          <t>SV-8278 (Design §6 validateForm() / S2-N1 / S2-N2)</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>SV-8278</t>
+          <t>SV-8278 (S2-R24 / §5-R6)</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>SV-8278</t>
+          <t>SV-8278 (S2-R27)</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>SV-8278</t>
+          <t>SV-8278 (S2-N1)</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>SV-8278</t>
+          <t>SV-8278 (S2-N2 / §5-R1)</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>SV-8279</t>
+          <t>SV-8279 (§5-R2 / S3 §3 discounts)</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>SV-8278</t>
+          <t>SV-8278 (§5-R4 / §5-R10 / S2-R3)</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>SV-8277, SV-8279</t>
+          <t>SV-8277,SV-8279 (S1-N1 / S3-R1b)</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>SV-8277, SV-8289</t>
+          <t>SV-8277,SV-8289 (S1-N2 / S13-R3 / S13-N2)</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>SV-8278</t>
+          <t>SV-8278 (S2-R41)</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>SV-8278, SV-8288</t>
+          <t>SV-8278,SV-8288 (S2-R33 / S12-R2)</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>SV-8278</t>
+          <t>SV-8278 (S2-R26, S2-R26a, §5-R15)</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>SV-8283</t>
+          <t>SV-8283 (S7-R12f / §5-R15)</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>SV-8287</t>
+          <t>SV-8287 (S11-R3 / S11-R4a / S11-R4b / §5-R15)</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>SV-8289</t>
+          <t>SV-8289 (SV-8456 Story 13)</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>SV-8289</t>
+          <t>SV-8289 (SV-8456 Story 13)</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
